--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486269_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486269_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2069</v>
+        <v>5.1868</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7428</v>
+        <v>4.476</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4642</v>
+        <v>0.7108</v>
       </c>
       <c r="G2" t="n">
         <v>1.1716</v>
@@ -610,13 +610,13 @@
         <v>3.0451</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.267</v>
+        <v>-0.2872</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.5744</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1082</v>
+        <v>-0.8616</v>
       </c>
       <c r="V2" t="n">
         <v>4.5199</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7722</v>
+        <v>2.544</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3578</v>
+        <v>2.3145</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4144</v>
+        <v>0.2295</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2769</v>
@@ -688,13 +688,13 @@
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09420000000000001</v>
+        <v>-0.134</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1334</v>
+        <v>-0.1766</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2276</v>
+        <v>0.0427</v>
       </c>
       <c r="V3" t="n">
         <v>3.3899</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4555</v>
+        <v>2.4953</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8205</v>
+        <v>0.7138</v>
       </c>
       <c r="F4" t="n">
-        <v>1.635</v>
+        <v>1.7816</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7764</v>
+        <v>0.852</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6788</v>
+        <v>0.4408</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.4552</v>
+        <v>0.4112</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.0017</v>
+        <v>2.1582</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4996</v>
+        <v>0.8577</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.5013</v>
+        <v>1.3005</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-1.3062</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1792</v>
+        <v>-0.4169</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9539</v>
+        <v>-0.8893</v>
       </c>
       <c r="P4" t="n">
         <v>2.6101</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6101</v>
+        <v>3.6976</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6218</v>
+        <v>-0.9668</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6922</v>
+        <v>-0.3569</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9296</v>
+        <v>-0.6099</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2736</v>
+        <v>2.1171</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8003</v>
+        <v>0.2105</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4733</v>
+        <v>1.9066</v>
       </c>
       <c r="G5" t="n">
-        <v>0.852</v>
+        <v>-0.0162</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4408</v>
+        <v>0.4627</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4112</v>
+        <v>-0.4789</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1582</v>
+        <v>1.855</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8577</v>
+        <v>0.7641</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3005</v>
+        <v>1.0909</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3062</v>
+        <v>-1.8712</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4169</v>
+        <v>-0.3013</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8893</v>
+        <v>-1.5698</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6101</v>
+        <v>2.3926</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6976</v>
+        <v>3.4801</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1885</v>
+        <v>-0.28</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2704</v>
+        <v>-0.2079</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9181</v>
+        <v>-0.0721</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.0207</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3095</v>
+        <v>1.323</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5971</v>
+        <v>1.8021</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9066</v>
+        <v>-0.4792</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0162</v>
+        <v>0.1802</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4627</v>
+        <v>2.205</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4789</v>
+        <v>-2.0248</v>
       </c>
       <c r="J6" t="n">
-        <v>1.855</v>
+        <v>2.4338</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7641</v>
+        <v>2.3573</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0909</v>
+        <v>0.0765</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8712</v>
+        <v>-2.2537</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3013</v>
+        <v>-0.1523</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5698</v>
+        <v>-2.1013</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4801</v>
+        <v>3.2626</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0875</v>
+        <v>0.0553</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0154</v>
+        <v>0.4134</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0721</v>
+        <v>-0.3581</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0207</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3491</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3698</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9509</v>
+        <v>1.2255</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5534</v>
+        <v>0.3302</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6024</v>
+        <v>0.8953</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1802</v>
+        <v>-1.7764</v>
       </c>
       <c r="H7" t="n">
-        <v>2.205</v>
+        <v>1.6788</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0248</v>
+        <v>-3.4552</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4338</v>
+        <v>-1.0017</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3573</v>
+        <v>1.4996</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0765</v>
+        <v>-2.5013</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2537</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1523</v>
+        <v>0.1792</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1013</v>
+        <v>-0.9539</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0875</v>
+        <v>2.6101</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.2626</v>
+        <v>2.6101</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3168</v>
+        <v>0.3918</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1646</v>
+        <v>0.2019</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4814</v>
+        <v>0.1899</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8336</v>
+        <v>-2.7296</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09080000000000001</v>
+        <v>-0.0209</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9244</v>
+        <v>-2.7087</v>
       </c>
       <c r="G8" t="n">
         <v>0.0784</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.7231</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0769</v>
+        <v>-0.1887</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7502</v>
+        <v>-0.5345</v>
       </c>
       <c r="V8" t="n">
         <v>-3.3899</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4796</v>
+        <v>-3.596</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4909</v>
+        <v>-2.4225</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9886</v>
+        <v>-1.1736</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0158</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0137</v>
+        <v>-0.1027</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2776</v>
+        <v>0.3461</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2639</v>
+        <v>-0.4488</v>
       </c>
       <c r="V9" t="n">
         <v>-1.13</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3565</v>
+        <v>-4.9481</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6626</v>
+        <v>-1.439</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.694</v>
+        <v>-3.509</v>
       </c>
       <c r="G10" t="n">
         <v>-2.71</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1267</v>
+        <v>0.2818</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4266</v>
+        <v>0.6501</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5533</v>
+        <v>-0.3683</v>
       </c>
       <c r="V10" t="n">
         <v>-3.3899</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.941</v>
+        <v>-6.5749</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.169</v>
+        <v>-4.8337</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.772</v>
+        <v>-1.7412</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0524</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-0.6324</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4675</v>
+        <v>-0.1322</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.531</v>
+        <v>-0.5002</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8902</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.642099999999997</v>
+        <v>-2.956900000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4459999999999997</v>
+        <v>1.130999999999998</v>
       </c>
       <c r="F12" t="n">
         <v>-4.087899999999999</v>
@@ -1375,7 +1375,7 @@
         <v>-11.7149</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6861000000000002</v>
+        <v>-0.6860999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-11.0286</v>
@@ -1390,13 +1390,13 @@
         <v>22.8382</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.0824</v>
+        <v>-2.3973</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4385999999999998</v>
+        <v>1.1236</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.521</v>
+        <v>-3.5209</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8695</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.1792</v>
+        <v>10.7977</v>
       </c>
       <c r="E13" t="n">
-        <v>9.709300000000001</v>
+        <v>10.6033</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5301</v>
+        <v>0.1943</v>
       </c>
       <c r="G13" t="n">
         <v>4.8224</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2931</v>
+        <v>0.3254</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5924</v>
+        <v>0.3016</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7007</v>
+        <v>0.0237</v>
       </c>
       <c r="V13" t="n">
         <v>5.6499</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8873</v>
+        <v>4.8865</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6712</v>
+        <v>3.2184</v>
       </c>
       <c r="F14" t="n">
-        <v>1.216</v>
+        <v>1.6682</v>
       </c>
       <c r="G14" t="n">
         <v>1.1693</v>
@@ -1546,13 +1546,13 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3259</v>
+        <v>1.3252</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6618</v>
+        <v>1.2089</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3359</v>
+        <v>0.1163</v>
       </c>
       <c r="V14" t="n">
         <v>1.3045</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. YU</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0876</v>
+        <v>0.2352</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8638</v>
+        <v>0.7781</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7762</v>
+        <v>-0.5429</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1421</v>
+        <v>5.1595</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2826</v>
+        <v>0.6141</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4247</v>
+        <v>4.5453</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3952</v>
+        <v>4.3037</v>
       </c>
       <c r="K15" t="n">
-        <v>0.949</v>
+        <v>0.0365</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5538</v>
+        <v>4.2672</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5372</v>
+        <v>0.8557</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6663</v>
+        <v>0.5776</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1291</v>
+        <v>0.2781</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.9576</v>
+        <v>-3.4801</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2626</v>
+        <v>-4.3501</v>
       </c>
       <c r="R15" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.882</v>
+        <v>0.2509</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8736</v>
+        <v>0.2596</v>
       </c>
       <c r="U15" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>1.13</v>
+        <v>-1.695</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6151</v>
+        <v>-0.3323</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1076</v>
+        <v>0.8613</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7227</v>
+        <v>-1.1935</v>
       </c>
       <c r="G16" t="n">
-        <v>5.1595</v>
+        <v>2.439</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6141</v>
+        <v>-2.4027</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5453</v>
+        <v>4.8417</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3037</v>
+        <v>4.2561</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0365</v>
+        <v>-0.392</v>
       </c>
       <c r="L16" t="n">
-        <v>4.2672</v>
+        <v>4.6481</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8557</v>
+        <v>-1.8171</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5776</v>
+        <v>-2.0107</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2781</v>
+        <v>0.1936</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.4801</v>
+        <v>-3.9151</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.3501</v>
+        <v>-5.4377</v>
       </c>
       <c r="R16" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5995</v>
+        <v>0.3836</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.411</v>
+        <v>0.1526</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1886</v>
+        <v>0.231</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.695</v>
+        <v>0.7602</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.8902</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>J. YU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7228</v>
+        <v>-0.6092</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8613</v>
+        <v>-1.5344</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.584</v>
+        <v>0.9252</v>
       </c>
       <c r="G17" t="n">
-        <v>2.439</v>
+        <v>-0.1421</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.4027</v>
+        <v>0.2826</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8417</v>
+        <v>-0.4247</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2561</v>
+        <v>0.3952</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.392</v>
+        <v>0.949</v>
       </c>
       <c r="L17" t="n">
-        <v>4.6481</v>
+        <v>-0.5538</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8171</v>
+        <v>-0.5372</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0107</v>
+        <v>-0.6663</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1936</v>
+        <v>0.1291</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.9151</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.4377</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0068</v>
+        <v>0.3605</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1526</v>
+        <v>0.2031</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1595</v>
+        <v>0.1574</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7602</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8902</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ MONTENEGRO</t>
+          <t>B. LUGARINI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8128</v>
+        <v>-0.9761</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5331</v>
+        <v>-0.5487</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2796</v>
+        <v>-0.4274</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4362</v>
+        <v>-0.526</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1589</v>
+        <v>-1.1986</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7228</v>
+        <v>0.6725</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0525</v>
+        <v>0.6106</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5411</v>
+        <v>0.5141</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5937</v>
+        <v>0.0964</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4887</v>
+        <v>-1.1366</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6178</v>
+        <v>-1.7127</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1291</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.3926</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3857</v>
+        <v>0.2025</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9167</v>
+        <v>-0.1142</v>
       </c>
       <c r="U18" t="n">
-        <v>0.469</v>
+        <v>0.3166</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7602</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
         <v>-1.13</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. LUGARINI</t>
+          <t>P. HERNANDEZ MONTENEGRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8688</v>
+        <v>-1.6618</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1075</v>
+        <v>-1.3155</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7614</v>
+        <v>-0.3464</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.526</v>
+        <v>-0.4362</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1986</v>
+        <v>-1.1589</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6725</v>
+        <v>0.7228</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6106</v>
+        <v>0.0525</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5141</v>
+        <v>-0.5411</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0964</v>
+        <v>0.5937</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1366</v>
+        <v>-0.4887</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7127</v>
+        <v>-0.6178</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.1291</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6525</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6903</v>
+        <v>1.5367</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6729000000000001</v>
+        <v>1.1344</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0173</v>
+        <v>0.4023</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0.7602</v>
       </c>
       <c r="X19" t="n">
         <v>-1.13</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DIAZ</t>
+          <t>S. RODRÍGUEZ RAMOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4406</v>
+        <v>-2.754</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.7788</v>
+        <v>-1.6126</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3382</v>
+        <v>-1.1414</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.076</v>
+        <v>-1.8444</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0919</v>
+        <v>0.1549</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0159</v>
+        <v>-1.9993</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5269</v>
+        <v>-1.9527</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2862</v>
+        <v>0.0912</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2407</v>
+        <v>-2.0439</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4509</v>
+        <v>0.1083</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1943</v>
+        <v>0.0636</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2566</v>
+        <v>0.0446</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9383</v>
+        <v>0.2629</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0769</v>
+        <v>0.3401</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0152</v>
+        <v>-0.0772</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.6504</v>
+        <v>-2.2599</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.6504</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ RAMOS</t>
+          <t>G. MARTINEZ DIAZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8766</v>
+        <v>-3.709</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2831</v>
+        <v>-4.6671</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5935</v>
+        <v>0.9581</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8444</v>
+        <v>-1.076</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1549</v>
+        <v>-1.0919</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9993</v>
+        <v>0.0159</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9527</v>
+        <v>-2.5269</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0912</v>
+        <v>-1.2862</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0439</v>
+        <v>-1.2407</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1083</v>
+        <v>1.4509</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0636</v>
+        <v>0.1943</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0446</v>
+        <v>1.2566</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0875</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8598</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3305</v>
+        <v>0.0349</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5294</v>
+        <v>0.6351</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2599</v>
+        <v>-2.6504</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2599</v>
+        <v>-2.6504</v>
       </c>
     </row>
     <row r="22">
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.642199999999999</v>
+        <v>5.877000000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>5.783100000000002</v>
+        <v>5.7828</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1409</v>
+        <v>0.09419999999999962</v>
       </c>
       <c r="G22" t="n">
-        <v>9.5655</v>
+        <v>9.565499999999998</v>
       </c>
       <c r="H22" t="n">
         <v>-5.7342</v>
@@ -2146,16 +2146,16 @@
         <v>11.7149</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6861999999999997</v>
+        <v>0.6861999999999999</v>
       </c>
       <c r="L22" t="n">
         <v>11.0287</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1493</v>
+        <v>-2.149299999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-6.4205</v>
+        <v>-6.420500000000001</v>
       </c>
       <c r="O22" t="n">
         <v>4.271</v>
@@ -2170,16 +2170,16 @@
         <v>11.9626</v>
       </c>
       <c r="S22" t="n">
-        <v>3.0824</v>
+        <v>5.3176</v>
       </c>
       <c r="T22" t="n">
         <v>3.521</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4387999999999997</v>
+        <v>1.7965</v>
       </c>
       <c r="V22" t="n">
-        <v>1.869499999999999</v>
+        <v>1.8695</v>
       </c>
       <c r="W22" t="n">
         <v>13.3852</v>
